--- a/data/trans_camb/IP16B05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Edad-trans_camb.xlsx
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,9</t>
+          <t>0,0; 53,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,36</t>
+          <t>0,0; 44,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,84</t>
+          <t>0,0; 27,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,35</t>
+          <t>0,0; 23,95</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,47</t>
+          <t>0,0; 114,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 98,85</t>
+          <t>0,0; 78,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,06</t>
+          <t>0,0; 37,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>0,0; 31,5</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 0,0</t>
+          <t>-34,91; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 0,0</t>
+          <t>-34,91; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 24,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,44</t>
+          <t>0,0; 28,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,95</t>
+          <t>-2,25; 10,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,17</t>
+          <t>0,0; 31,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 40,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 11,04</t>
+          <t>-2,25; 11,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,34</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Edad-trans_camb.xlsx
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,37</t>
+          <t>0,0; 49,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,0</t>
+          <t>0,0; 54,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,11</t>
+          <t>0,0; 25,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,95</t>
+          <t>0,0; 25,61</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 114,47</t>
+          <t>0,0; 101,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,57</t>
+          <t>0,0; 121,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,44</t>
+          <t>0,0; 34,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,5</t>
+          <t>0,0; 34,47</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 0,0</t>
+          <t>-35,13; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 0,0</t>
+          <t>-35,13; 0,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,09</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,67</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,6</t>
+          <t>-2,93; 9,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,81</t>
+          <t>0,0; 13,66</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,74</t>
+          <t>0,0; 34,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,29</t>
+          <t>0,0; 43,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 11,94</t>
+          <t>-2,93; 10,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
     </row>
